--- a/sample data/reviews_data.xlsx
+++ b/sample data/reviews_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linkedin/Documents/ETL_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e9467eb25b74a64/study things/projects/E-commerce DB/sample data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4101263F-B52B-C84C-B1EC-9A9593041668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4101263F-B52B-C84C-B1EC-9A9593041668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDB74A76-C1AD-4CF2-BF4C-6F39D7770EF4}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -406,13 +406,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -426,7 +426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>27</v>
       </c>
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>20</v>
       </c>
@@ -454,7 +454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>24</v>
       </c>
@@ -468,7 +468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>12</v>
       </c>
@@ -482,7 +482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>50</v>
       </c>
@@ -496,7 +496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>35</v>
       </c>
@@ -510,7 +510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>60</v>
       </c>
@@ -524,7 +524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>33</v>
       </c>
@@ -535,7 +535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>33</v>
       </c>
@@ -549,7 +549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>51</v>
       </c>
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>43</v>
       </c>
@@ -577,7 +577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>37</v>
       </c>
@@ -591,7 +591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3</v>
       </c>
@@ -619,7 +619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
@@ -630,7 +630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>33</v>
       </c>
@@ -644,7 +644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>40</v>
       </c>
@@ -658,7 +658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>10</v>
       </c>
@@ -672,7 +672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>43</v>
       </c>
@@ -686,7 +686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>44</v>
       </c>
@@ -700,7 +700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>29</v>
       </c>
@@ -714,7 +714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>13</v>
       </c>
@@ -725,7 +725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>12</v>
       </c>
@@ -739,7 +739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>31</v>
       </c>
@@ -753,7 +753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>46</v>
       </c>
@@ -767,7 +767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2</v>
       </c>
@@ -781,7 +781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>51</v>
       </c>
@@ -795,7 +795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>50</v>
       </c>
@@ -809,7 +809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>35</v>
       </c>
@@ -820,7 +820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>23</v>
       </c>
@@ -834,7 +834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>17</v>
       </c>
@@ -848,7 +848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>26</v>
       </c>
@@ -862,7 +862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>8</v>
       </c>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>29</v>
       </c>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>26</v>
       </c>
@@ -904,7 +904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>10</v>
       </c>
@@ -915,7 +915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>26</v>
       </c>
@@ -929,7 +929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>34</v>
       </c>
@@ -943,7 +943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>51</v>
       </c>
@@ -957,7 +957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>41</v>
       </c>
@@ -971,7 +971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>7</v>
       </c>
@@ -985,7 +985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>4</v>
       </c>
@@ -999,7 +999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>58</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>53</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>50</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>11</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>29</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>56</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>36</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>25</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>21</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>57</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>36</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>10</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>37</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>9</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>24</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>35</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>49</v>
       </c>
